--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:20</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -742,7 +742,7 @@
         <v>0.47</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
@@ -756,7 +756,7 @@
         <v>0.09</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18">
@@ -770,7 +770,7 @@
         <v>0.41</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19">
@@ -784,7 +784,7 @@
         <v>0.26</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:11</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -515,7 +515,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_i_peringr_median_a_2021.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
